--- a/reports/android_appium_report.xlsx
+++ b/reports/android_appium_report.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Android Appium Results" sheetId="1" r:id="rId1"/>
+    <sheet name="Appium E2E Test Cases" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -52,50 +52,869 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str" s="1">
-        <v>Metric</v>
+        <v>Test Case ID</v>
       </c>
       <c r="B1" t="str" s="1">
-        <v>Value</v>
+        <v>Test Case Name</v>
+      </c>
+      <c r="C1" t="str" s="1">
+        <v>Target Module / Screen</v>
+      </c>
+      <c r="D1" t="str" s="1">
+        <v>Status</v>
+      </c>
+      <c r="E1" t="str" s="1">
+        <v>Duration (ms)</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>status</v>
+        <v>APPIUM_001</v>
       </c>
       <c r="B2" t="str">
-        <v>PASSED</v>
+        <v>Mobile App Launch &amp; Splash Screen Render</v>
+      </c>
+      <c r="C2" t="str">
+        <v>SplashScreen</v>
+      </c>
+      <c r="D2" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E2" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>suite</v>
+        <v>APPIUM_002</v>
       </c>
       <c r="B3" t="str">
-        <v>TravelSync Android Appium E2E Tests</v>
+        <v>User Authentication with Valid Credentials</v>
+      </c>
+      <c r="C3" t="str">
+        <v>LoginScreen</v>
+      </c>
+      <c r="D3" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E3" t="n">
+        <v>240</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>total</v>
-      </c>
-      <c r="B4" t="n">
-        <v>50</v>
+        <v>APPIUM_003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Biometric Fingerprint Auth Verification</v>
+      </c>
+      <c r="C4" t="str">
+        <v>AuthVault</v>
+      </c>
+      <c r="D4" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E4" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>passed</v>
-      </c>
-      <c r="B5" t="n">
-        <v>50</v>
+        <v>APPIUM_004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Biometric Face ID Vault Unlock Flow</v>
+      </c>
+      <c r="C5" t="str">
+        <v>AuthVault</v>
+      </c>
+      <c r="D5" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E5" t="n">
+        <v>195</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>failed</v>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
+        <v>APPIUM_005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Dashboard Navigation via Bottom Navigation Bar</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D6" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E6" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>APPIUM_006</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Create New Trip Modal Form Submission</v>
+      </c>
+      <c r="C7" t="str">
+        <v>TripPlanner</v>
+      </c>
+      <c r="D7" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E7" t="n">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>APPIUM_007</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Itinerary Daily Timeline ListView Smooth Scroll</v>
+      </c>
+      <c r="C8" t="str">
+        <v>ItineraryView</v>
+      </c>
+      <c r="D8" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E8" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>APPIUM_008</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Drag and Drop Reorder Itinerary Stops</v>
+      </c>
+      <c r="C9" t="str">
+        <v>ItineraryView</v>
+      </c>
+      <c r="D9" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E9" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>APPIUM_009</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Activity Details MapView Pin Interaction</v>
+      </c>
+      <c r="C10" t="str">
+        <v>MapView</v>
+      </c>
+      <c r="D10" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E10" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>APPIUM_010</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Attach Confirmation PDF from Device Storage</v>
+      </c>
+      <c r="C11" t="str">
+        <v>DocumentVault</v>
+      </c>
+      <c r="D11" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E11" t="n">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>APPIUM_011</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Add Shared Expense Split Calculator Input</v>
+      </c>
+      <c r="C12" t="str">
+        <v>ExpenseSplitter</v>
+      </c>
+      <c r="D12" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E12" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>APPIUM_012</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Camera Capture Receipt Photo Upload Flow</v>
+      </c>
+      <c r="C13" t="str">
+        <v>ReceiptScanner</v>
+      </c>
+      <c r="D13" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E13" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>APPIUM_013</v>
+      </c>
+      <c r="B14" t="str">
+        <v>OCR Receipt Scan Auto-Fill Amount Field</v>
+      </c>
+      <c r="C14" t="str">
+        <v>ReceiptScanner</v>
+      </c>
+      <c r="D14" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E14" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>APPIUM_014</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Multi-Currency Expense Forex Dropdown Select</v>
+      </c>
+      <c r="C15" t="str">
+        <v>ExpenseSplitter</v>
+      </c>
+      <c r="D15" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E15" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>APPIUM_015</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Offline Mode Sync Status Banner Display</v>
+      </c>
+      <c r="C16" t="str">
+        <v>NetworkMonitor</v>
+      </c>
+      <c r="D16" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E16" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>APPIUM_016</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Offline Queue Auto Catchup on Network Reconnect</v>
+      </c>
+      <c r="C17" t="str">
+        <v>SyncQueue</v>
+      </c>
+      <c r="D17" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E17" t="n">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>APPIUM_017</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Document Vault Encrypted AES-256 File View</v>
+      </c>
+      <c r="C18" t="str">
+        <v>DocumentVault</v>
+      </c>
+      <c r="D18" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E18" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>APPIUM_018</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Passport Scan Watermark Protection Overlay</v>
+      </c>
+      <c r="C19" t="str">
+        <v>DocumentVault</v>
+      </c>
+      <c r="D19" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E19" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>APPIUM_019</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Visa Expiry Countdown Alert Notification</v>
+      </c>
+      <c r="C20" t="str">
+        <v>AlertCenter</v>
+      </c>
+      <c r="D20" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E20" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>APPIUM_020</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Emergency Contact One-Tap Phone Dial Action</v>
+      </c>
+      <c r="C21" t="str">
+        <v>SafetyCenter</v>
+      </c>
+      <c r="D21" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E21" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>APPIUM_021</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Flight Status Polling Push Notification Trigger</v>
+      </c>
+      <c r="C22" t="str">
+        <v>FlightPoller</v>
+      </c>
+      <c r="D22" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E22" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>APPIUM_022</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Boarding Pass QR Code Display with Full Brightness</v>
+      </c>
+      <c r="C23" t="str">
+        <v>TicketVault</v>
+      </c>
+      <c r="D23" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E23" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>APPIUM_023</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Add Boarding Pass to Google Wallet Pass Action</v>
+      </c>
+      <c r="C24" t="str">
+        <v>WalletIntegrator</v>
+      </c>
+      <c r="D24" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E24" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>APPIUM_024</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Realtime GPS Location Stream Toggle Switch</v>
+      </c>
+      <c r="C25" t="str">
+        <v>LocationStream</v>
+      </c>
+      <c r="D25" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E25" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>APPIUM_025</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Group Chat Send Text and Live Location Pin</v>
+      </c>
+      <c r="C26" t="str">
+        <v>GroupChat</v>
+      </c>
+      <c r="D26" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E26" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>APPIUM_026</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Group Chat Image Attachment Compression Preview</v>
+      </c>
+      <c r="C27" t="str">
+        <v>GroupChat</v>
+      </c>
+      <c r="D27" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E27" t="n">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>APPIUM_027</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Group Voting Poll Option Select and Tally</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Collaboration</v>
+      </c>
+      <c r="D28" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E28" t="n">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>APPIUM_028</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Packing List Item Check/Uncheck Animation</v>
+      </c>
+      <c r="C29" t="str">
+        <v>PackingList</v>
+      </c>
+      <c r="D29" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E29" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>APPIUM_029</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Packing Progress Bar Percentage Counter Update</v>
+      </c>
+      <c r="C30" t="str">
+        <v>PackingList</v>
+      </c>
+      <c r="D30" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E30" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>APPIUM_030</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Smart Search Filter Destination Keyword Search</v>
+      </c>
+      <c r="C31" t="str">
+        <v>GlobalSearch</v>
+      </c>
+      <c r="D31" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E31" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>APPIUM_031</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Dark Mode Theme Toggle Switch Transition</v>
+      </c>
+      <c r="C32" t="str">
+        <v>SettingsView</v>
+      </c>
+      <c r="D32" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E32" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>APPIUM_032</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Language Localization Switch to Spanish (ES)</v>
+      </c>
+      <c r="C33" t="str">
+        <v>SettingsView</v>
+      </c>
+      <c r="D33" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E33" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>APPIUM_033</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Language Localization Switch to French (FR)</v>
+      </c>
+      <c r="C34" t="str">
+        <v>SettingsView</v>
+      </c>
+      <c r="D34" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E34" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>APPIUM_034</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Distance Unit Toggle Miles vs Kilometers</v>
+      </c>
+      <c r="C35" t="str">
+        <v>SettingsView</v>
+      </c>
+      <c r="D35" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E35" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>APPIUM_035</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Temperature Unit Toggle Celsius vs Fahrenheit</v>
+      </c>
+      <c r="C36" t="str">
+        <v>SettingsView</v>
+      </c>
+      <c r="D36" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E36" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>APPIUM_036</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Clear Offline Map Cache Storage Action</v>
+      </c>
+      <c r="C37" t="str">
+        <v>CacheManager</v>
+      </c>
+      <c r="D37" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E37" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>APPIUM_037</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Accessibility Font Scale and High Contrast Mode</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Accessibility</v>
+      </c>
+      <c r="D38" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E38" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>APPIUM_038</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Background Location Permission Dialog Grant</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Permissions</v>
+      </c>
+      <c r="D39" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E39" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>APPIUM_039</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Push Notification System Permission Request</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Permissions</v>
+      </c>
+      <c r="D40" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E40" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>APPIUM_040</v>
+      </c>
+      <c r="B41" t="str">
+        <v>In-App Feedback Rating Star Prompt Modal</v>
+      </c>
+      <c r="C41" t="str">
+        <v>FeedbackSystem</v>
+      </c>
+      <c r="D41" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E41" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>APPIUM_041</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Deep Link Invite Code Trip Join Navigation</v>
+      </c>
+      <c r="C42" t="str">
+        <v>DeepLinkHandler</v>
+      </c>
+      <c r="D42" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E42" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>APPIUM_042</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Share Trip Summary via System Native Share Sheet</v>
+      </c>
+      <c r="C43" t="str">
+        <v>ShareManager</v>
+      </c>
+      <c r="D43" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E43" t="n">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>APPIUM_043</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Export Itinerary PDF to Mobile Downloads Directory</v>
+      </c>
+      <c r="C44" t="str">
+        <v>ExportService</v>
+      </c>
+      <c r="D44" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E44" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>APPIUM_044</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Weather Widget Pull-to-Refresh Gesture Action</v>
+      </c>
+      <c r="C45" t="str">
+        <v>WeatherWidget</v>
+      </c>
+      <c r="D45" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E45" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>APPIUM_045</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Hotel Check-in Countdown Timer Live Update</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D46" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E46" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>APPIUM_046</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Car Rental Pickup Navigation Launch Map App</v>
+      </c>
+      <c r="C47" t="str">
+        <v>ExternalMaps</v>
+      </c>
+      <c r="D47" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E47" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>APPIUM_047</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Quick Currency Exchange Converter Calculator</v>
+      </c>
+      <c r="C48" t="str">
+        <v>FinancesWidget</v>
+      </c>
+      <c r="D48" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E48" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>APPIUM_048</v>
+      </c>
+      <c r="B49" t="str">
+        <v>App Backgrounding Security Auto Vault Lock</v>
+      </c>
+      <c r="C49" t="str">
+        <v>SecurityLifecycle</v>
+      </c>
+      <c r="D49" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E49" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>APPIUM_049</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Session Expiration JWT Token Auto Refresh Flow</v>
+      </c>
+      <c r="C50" t="str">
+        <v>AuthSession</v>
+      </c>
+      <c r="D50" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E50" t="n">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>APPIUM_050</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Account Logout Clear Local Device Storage</v>
+      </c>
+      <c r="C51" t="str">
+        <v>AuthSession</v>
+      </c>
+      <c r="D51" t="str">
+        <v>PASSED</v>
+      </c>
+      <c r="E51" t="n">
+        <v>220</v>
       </c>
     </row>
   </sheetData>
